--- a/ETF净流动数据.xlsx
+++ b/ETF净流动数据.xlsx
@@ -543,7 +543,7 @@
         <v>-983.7540001</v>
       </c>
       <c r="C2" t="n">
-        <v>-5834.537840700002</v>
+        <v>-5834.5378407</v>
       </c>
       <c r="D2" t="n">
         <v>-356.769198</v>
@@ -605,7 +605,7 @@
         <v>-213.836268</v>
       </c>
       <c r="E4" t="n">
-        <v>6.001254500000003</v>
+        <v>6.001254499999999</v>
       </c>
       <c r="F4" t="n">
         <v>-77.9807277</v>
@@ -630,7 +630,7 @@
         <v>-562.7977997999997</v>
       </c>
       <c r="D5" t="n">
-        <v>-355.6247340000001</v>
+        <v>-355.624734</v>
       </c>
       <c r="E5" t="n">
         <v>-299.802996</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.27055129999999</v>
+        <v>23.2705513</v>
       </c>
       <c r="C8" t="n">
         <v>452.6137938</v>
@@ -823,7 +823,7 @@
         <v>-1400.86880044</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-8224.146480000001</v>
+        <v>-8224.146479999999</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>-927.1749070000003</v>
@@ -1116,7 +1116,7 @@
         <v>-142.0243285</v>
       </c>
       <c r="E6" t="n">
-        <v>3.949652499999999</v>
+        <v>3.9496525</v>
       </c>
       <c r="F6" t="n">
         <v>-8.848926499999999</v>
@@ -1205,7 +1205,7 @@
         <v>0.2441485</v>
       </c>
       <c r="H8" t="n">
-        <v>5.31937242478</v>
+        <v>5.319372424779999</v>
       </c>
       <c r="I8" t="n">
         <v>-0.204751</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-5834.537840700002</v>
+        <v>-5834.5378407</v>
       </c>
       <c r="E7" t="n">
         <v>29</v>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6.001254500000003</v>
+        <v>6.001254499999999</v>
       </c>
       <c r="E22" t="n">
         <v>56</v>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-355.6247340000001</v>
+        <v>-355.624734</v>
       </c>
       <c r="E27" t="n">
         <v>39</v>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>23.27055129999999</v>
+        <v>23.2705513</v>
       </c>
       <c r="E44" t="n">
         <v>12</v>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3.949652499999999</v>
+        <v>3.9496525</v>
       </c>
       <c r="E117" t="n">
         <v>25</v>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>5.31937242478</v>
+        <v>5.319372424779999</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>9.170880659669001</v>
+        <v>9.170880659668999</v>
       </c>
       <c r="E184" t="n">
         <v>17</v>
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>-0.2371225000000001</v>
+        <v>-0.2371225000000002</v>
       </c>
       <c r="E201" t="n">
         <v>14</v>
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.5971957999999998</v>
+        <v>0.5971958000000001</v>
       </c>
       <c r="E209" t="n">
         <v>10</v>
@@ -6824,7 +6824,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>32.51484755043</v>
+        <v>32.51484755043001</v>
       </c>
       <c r="E212" t="n">
         <v>17</v>
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>-2.908035504</v>
+        <v>-2.908035504000001</v>
       </c>
       <c r="E219" t="n">
         <v>46</v>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>-0.8517574999999997</v>
+        <v>-0.8517574999999999</v>
       </c>
       <c r="E223" t="n">
         <v>11</v>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>-5.262118000000001</v>
+        <v>-5.262118</v>
       </c>
       <c r="E240" t="n">
         <v>17</v>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>7.115723249999999</v>
+        <v>7.11572325</v>
       </c>
       <c r="E266" t="n">
         <v>22</v>
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>-9.751320499999993</v>
+        <v>-9.751320499999991</v>
       </c>
       <c r="E294" t="n">
         <v>22</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>-0.8732807499999998</v>
+        <v>-0.8732807500000001</v>
       </c>
       <c r="E319" t="n">
         <v>9</v>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>18.48807050000001</v>
+        <v>18.4880705</v>
       </c>
       <c r="E328" t="n">
         <v>18</v>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>-0.9297368999999998</v>
+        <v>-0.9297369</v>
       </c>
       <c r="E339" t="n">
         <v>25</v>
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>0.8580855000000006</v>
+        <v>0.8580854999999999</v>
       </c>
       <c r="E346" t="n">
         <v>3</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0.7097340000000002</v>
+        <v>0.709734</v>
       </c>
       <c r="E360" t="n">
         <v>7</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>-0.8162852543969991</v>
+        <v>-0.8162852543969988</v>
       </c>
       <c r="E364" t="n">
         <v>25</v>
@@ -10872,7 +10872,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0.5514594999999999</v>
+        <v>0.5514595</v>
       </c>
       <c r="E388" t="n">
         <v>7</v>
@@ -11424,7 +11424,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>-6.721443400000003</v>
+        <v>-6.7214434</v>
       </c>
       <c r="E412" t="n">
         <v>18</v>
@@ -11792,7 +11792,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>-0.1719256999999998</v>
+        <v>-0.1719257</v>
       </c>
       <c r="E428" t="n">
         <v>26</v>
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>7.8375235</v>
+        <v>7.838823</v>
       </c>
       <c r="E435" t="n">
         <v>11</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>-0.83135</v>
+        <v>-0.8313500000000001</v>
       </c>
       <c r="E439" t="n">
         <v>23</v>
@@ -12068,7 +12068,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>-0.3685520999999988</v>
+        <v>-0.3685520999999991</v>
       </c>
       <c r="E440" t="n">
         <v>18</v>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>0.9284854000000001</v>
+        <v>0.9284854</v>
       </c>
       <c r="E465" t="n">
         <v>11</v>
@@ -12827,7 +12827,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>-4.152141999999999</v>
+        <v>-4.152142</v>
       </c>
       <c r="E473" t="n">
         <v>29</v>
@@ -12965,7 +12965,7 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>85.11167146400001</v>
+        <v>85.111671464</v>
       </c>
       <c r="E479" t="n">
         <v>29</v>
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>-0.08934260000000015</v>
+        <v>-0.08934259999999999</v>
       </c>
       <c r="E482" t="n">
         <v>6</v>
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>2.959772799999999</v>
+        <v>2.9597728</v>
       </c>
       <c r="E483" t="n">
         <v>11</v>
@@ -13955,7 +13955,7 @@
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -14440,7 +14440,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7.593334</v>
+        <v>7.5946335</v>
       </c>
       <c r="E21" t="n">
         <v>11</v>
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.4632119999999998</v>
+        <v>-0.463212</v>
       </c>
       <c r="E22" t="n">
         <v>17</v>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.2495011999999999</v>
+        <v>0.2495012</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
@@ -14900,7 +14900,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-0.03987100000000004</v>
+        <v>-0.039871</v>
       </c>
       <c r="E41" t="n">
         <v>10</v>
@@ -14923,7 +14923,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.1322375000000001</v>
+        <v>0.1322375</v>
       </c>
       <c r="E42" t="n">
         <v>26</v>
@@ -37525,7 +37525,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -37939,7 +37939,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>-0.06792100000000002</v>
+        <v>-0.067921</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9823220000000003</v>
+        <v>0.982322</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.07268800000000003</v>
+        <v>0.072688</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.2925375000000001</v>
+        <v>0.2925375</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.007552500000000018</v>
+        <v>0.0075525</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.7622910000000003</v>
+        <v>0.7622910000000006</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.06822599999999998</v>
+        <v>0.06822599999999999</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -40424,7 +40424,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>-0.8624370000000001</v>
+        <v>-0.862437</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6.428967</v>
+        <v>6.428967000000001</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>-69.25461600000003</v>
+        <v>-69.25461600000001</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>-106.0944659999999</v>
+        <v>-106.094466</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>-0.02275499999999994</v>
+        <v>-0.02275499999999996</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>-0.8270519999999999</v>
+        <v>-0.827052</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2.882700000000001</v>
+        <v>2.8827</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.2527349009999989</v>
+        <v>0.2527349009999991</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.3866820000000002</v>
+        <v>0.3866820000000003</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>-0.06878300000000002</v>
+        <v>-0.068783</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>-0.5052929999999999</v>
+        <v>-0.505293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>-0.09721199999999985</v>
+        <v>-0.09721200000000001</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>-0.07308199999999997</v>
+        <v>-0.07308199999999999</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>-0.07078899999999999</v>
+        <v>-0.070789</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>0.4513829999999999</v>
+        <v>0.451383</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>-0.04651499999999999</v>
+        <v>-0.04651500000000002</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -48684,7 +48684,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>0.9612539999999998</v>
+        <v>0.9612540000000001</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>52.79206949999999</v>
+        <v>52.79206949999998</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>0.2458359999999999</v>
+        <v>0.245836</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>-0.05132800000000001</v>
+        <v>-0.051328</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>0.01553475000000002</v>
+        <v>0.01553475</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>5.655687</v>
+        <v>5.655936</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>4.255662</v>
+        <v>4.256512</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -49279,7 +49279,7 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>-0.001488000000000002</v>
+        <v>-0.001488</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>109.55554</v>
+        <v>109.555637</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>-0.7052925</v>
+        <v>-0.705189</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>-0.4256400000000001</v>
+        <v>-0.42564</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>-6.323259000000001</v>
+        <v>-6.323259</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>0.03779099999999999</v>
+        <v>0.037791</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         </is>
       </c>
       <c r="E392" t="n">
-        <v>0.03714500000000002</v>
+        <v>0.03714500000000001</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         </is>
       </c>
       <c r="E402" t="n">
-        <v>-5.153964999999999</v>
+        <v>-5.153965</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -51694,7 +51694,7 @@
         </is>
       </c>
       <c r="E405" t="n">
-        <v>-0.04621050000000002</v>
+        <v>-0.0462105</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         </is>
       </c>
       <c r="E411" t="n">
-        <v>-0.05024699999999999</v>
+        <v>-0.050247</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         </is>
       </c>
       <c r="E427" t="n">
-        <v>0.02092299999999999</v>
+        <v>0.020923</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         </is>
       </c>
       <c r="E452" t="n">
-        <v>-1.807334000000001</v>
+        <v>-1.807334</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -53479,7 +53479,7 @@
         </is>
       </c>
       <c r="E456" t="n">
-        <v>0.01524299999999999</v>
+        <v>0.015243</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>-0.01168000000000002</v>
+        <v>-0.01168</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -53619,7 +53619,7 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>0.002273700000000002</v>
+        <v>0.0022737</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>-0.01611000000000001</v>
+        <v>-0.01611</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>0.4133459999999998</v>
+        <v>0.413346</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -54914,7 +54914,7 @@
         </is>
       </c>
       <c r="E497" t="n">
-        <v>67.75699340919999</v>
+        <v>67.75699340920001</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -54984,7 +54984,7 @@
         </is>
       </c>
       <c r="E499" t="n">
-        <v>5.295742000000003</v>
+        <v>5.295742000000002</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -55754,7 +55754,7 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>0.4255883479999998</v>
+        <v>0.4255883479999995</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         </is>
       </c>
       <c r="E548" t="n">
-        <v>-0.02709899999999999</v>
+        <v>-0.02709900000000001</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -58274,7 +58274,7 @@
         </is>
       </c>
       <c r="E593" t="n">
-        <v>0.2731604999999997</v>
+        <v>0.2731605</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -59324,7 +59324,7 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>0.02011600000000001</v>
+        <v>0.020116</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>5.183135599999999</v>
+        <v>5.1831356</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -60409,7 +60409,7 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>-0.05073400000000001</v>
+        <v>-0.050734</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -60444,7 +60444,7 @@
         </is>
       </c>
       <c r="E655" t="n">
-        <v>0.03025900000000001</v>
+        <v>0.030259</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
         </is>
       </c>
       <c r="E660" t="n">
-        <v>-0.005866999999999982</v>
+        <v>-0.005867</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>0.486218</v>
+        <v>0.4862180000000002</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -60759,7 +60759,7 @@
         </is>
       </c>
       <c r="E664" t="n">
-        <v>0.5638199835000001</v>
+        <v>0.5638199835</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -61074,7 +61074,7 @@
         </is>
       </c>
       <c r="E673" t="n">
-        <v>-3.718595000000001</v>
+        <v>-3.718595000000005</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -61249,7 +61249,7 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>0.5661829999999999</v>
+        <v>0.566183</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -62404,7 +62404,7 @@
         </is>
       </c>
       <c r="E711" t="n">
-        <v>-0.07867299999999999</v>
+        <v>-0.07867300000000001</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>8.087883</v>
+        <v>8.087883000000001</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64189,7 +64189,7 @@
         </is>
       </c>
       <c r="E762" t="n">
-        <v>-0.07713150000000014</v>
+        <v>-0.07713150000000001</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -64644,7 +64644,7 @@
         </is>
       </c>
       <c r="E775" t="n">
-        <v>0.009105</v>
+        <v>0.009104999999999995</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>0.05301500000000008</v>
+        <v>0.053015</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -65834,7 +65834,7 @@
         </is>
       </c>
       <c r="E809" t="n">
-        <v>0.06686800000000015</v>
+        <v>0.066868</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -66845,9 +66845,9 @@
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -66855,12 +66855,12 @@
     <col width="21" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="21" customWidth="1" min="23" max="23"/>
@@ -67032,7 +67032,7 @@
         <v>11.1572772</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5971957999999998</v>
+        <v>0.5971958000000001</v>
       </c>
       <c r="E2" t="n">
         <v>20.32604075</v>
@@ -67056,7 +67056,7 @@
         <v>127.9147005</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2371225000000001</v>
+        <v>-0.2371225000000002</v>
       </c>
       <c r="M2" t="n">
         <v>256.7420511</v>
@@ -67071,7 +67071,7 @@
         <v>12.8131059</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.170880659669001</v>
+        <v>9.170880659668999</v>
       </c>
       <c r="R2" t="n">
         <v>15.2265605</v>
@@ -67132,7 +67132,7 @@
         <v>-5.1136105</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8517574999999997</v>
+        <v>-0.8517574999999999</v>
       </c>
       <c r="H3" t="n">
         <v>-26.164993</v>
@@ -67150,7 +67150,7 @@
         <v>-2.248627</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.908035504</v>
+        <v>-2.908035504000001</v>
       </c>
       <c r="N3" t="n">
         <v>-8.996258499999998</v>
@@ -67162,7 +67162,7 @@
         <v>73.72734545</v>
       </c>
       <c r="Q3" t="n">
-        <v>32.51484755043</v>
+        <v>32.51484755043001</v>
       </c>
       <c r="R3" t="n">
         <v>8.9124012</v>
@@ -67253,7 +67253,7 @@
         <v>20.97881655</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.262118000000001</v>
+        <v>-5.262118</v>
       </c>
       <c r="R4" t="n">
         <v>7.0143598</v>
@@ -67335,7 +67335,7 @@
         <v>-274.734009082</v>
       </c>
       <c r="N5" t="n">
-        <v>7.115723249999999</v>
+        <v>7.11572325</v>
       </c>
       <c r="O5" t="n">
         <v>-77.61164049999999</v>
@@ -67399,7 +67399,7 @@
         <v>-2.3913362</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8732807499999998</v>
+        <v>-0.8732807500000001</v>
       </c>
       <c r="F6" t="n">
         <v>-15.0389935</v>
@@ -67426,7 +67426,7 @@
         <v>-85.58123610000004</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.751320499999993</v>
+        <v>-9.751320499999991</v>
       </c>
       <c r="O6" t="n">
         <v>-5.849002475999999</v>
@@ -67481,10 +67481,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8580855000000006</v>
+        <v>0.8580854999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>18.48807050000001</v>
+        <v>18.4880705</v>
       </c>
       <c r="D7" t="n">
         <v>5.8472767</v>
@@ -67535,7 +67535,7 @@
         <v>39.50987269999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9297368999999998</v>
+        <v>-0.9297369</v>
       </c>
       <c r="U7" t="n">
         <v>-37.12666539309599</v>
@@ -67590,7 +67590,7 @@
         <v>-3.9061835</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8162852543969991</v>
+        <v>-0.8162852543969988</v>
       </c>
       <c r="I8" t="n">
         <v>28.71959319999999</v>
@@ -67635,7 +67635,7 @@
         <v>0.414329</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7097340000000002</v>
+        <v>0.709734</v>
       </c>
       <c r="X8" t="n">
         <v>8.8489425</v>
@@ -67726,7 +67726,7 @@
         <v>-0.240134</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5514594999999999</v>
+        <v>0.5514595</v>
       </c>
       <c r="X9" t="n">
         <v>10.064735</v>
@@ -67757,7 +67757,7 @@
         <v>1.4675135</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.721443400000003</v>
+        <v>-6.7214434</v>
       </c>
       <c r="D10" t="n">
         <v>-7.8162503</v>
@@ -67793,7 +67793,7 @@
         <v>2.792995999999992</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1719256999999998</v>
+        <v>-0.1719257</v>
       </c>
       <c r="P10" t="n">
         <v>8.886001500000001</v>
@@ -67848,7 +67848,7 @@
         <v>-0.4530615</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3685520999999988</v>
+        <v>-0.3685520999999991</v>
       </c>
       <c r="D11" t="n">
         <v>7.3097422</v>
@@ -67887,13 +67887,13 @@
         <v>10.9041997</v>
       </c>
       <c r="P11" t="n">
-        <v>7.8375235</v>
+        <v>7.838823</v>
       </c>
       <c r="Q11" t="n">
         <v>10.010849</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.83135</v>
+        <v>-0.8313500000000001</v>
       </c>
       <c r="S11" t="n">
         <v>13.5946646</v>
@@ -67951,7 +67951,7 @@
         <v>-44.7607295</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-86.54751049999999</v>
+        <v>-86.5475105</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>-120.927231207767</v>
@@ -67978,10 +67978,10 @@
         <v>126.9985336338</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>122.00312385</v>
+        <v>122.00442335</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>-37.29853659360301</v>
+        <v>-37.298536593603</v>
       </c>
       <c r="R12" s="2" t="n">
         <v>68.921375140687</v>
@@ -68634,7 +68634,7 @@
         <v>2.7849463</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.107274</v>
+        <v>0.1085735</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>2.2765235</v>
@@ -68701,7 +68701,7 @@
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -68793,7 +68793,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.593334</v>
+        <v>7.5946335</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
@@ -68883,7 +68883,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.2495011999999999</v>
+        <v>0.2495012</v>
       </c>
       <c r="D10" t="n">
         <v>23</v>
@@ -68901,7 +68901,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1322375000000001</v>
+        <v>0.1322375</v>
       </c>
       <c r="D11" t="n">
         <v>26</v>
@@ -68919,7 +68919,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.03987100000000004</v>
+        <v>-0.039871</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -69009,7 +69009,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.4632119999999998</v>
+        <v>-0.463212</v>
       </c>
       <c r="D17" t="n">
         <v>17</v>
@@ -69248,10 +69248,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -69308,7 +69308,7 @@
         <v>3.0810721</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9284854000000001</v>
+        <v>0.9284854</v>
       </c>
       <c r="F2" t="n">
         <v>30.561943</v>
@@ -69336,7 +69336,7 @@
         <v>1.2138496</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.152141999999999</v>
+        <v>-4.152142</v>
       </c>
       <c r="G3" t="n">
         <v>-9.229405399999999</v>
@@ -69361,7 +69361,7 @@
         <v>5.4853856</v>
       </c>
       <c r="F4" t="n">
-        <v>85.11167146400001</v>
+        <v>85.111671464</v>
       </c>
       <c r="G4" t="n">
         <v>4.95121944</v>
@@ -69377,13 +69377,13 @@
         <v>-2.5846868</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.08934260000000015</v>
+        <v>-0.08934259999999999</v>
       </c>
       <c r="D5" t="n">
         <v>24.78687630000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2.959772799999999</v>
+        <v>2.9597728</v>
       </c>
       <c r="F5" t="n">
         <v>52.2592015</v>
